--- a/stories/arbres/ATOM-EMO.LEX.005-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ferdinand dessine un bateau à la table. Maman coupe des carottes. Le crayon bleu glisse. Sa sœur Clara prend le crayon. Ferdinand sent son visage chaud. Son ventre est dur. Ferdinand dit : je suis en colère. Il ouvre les doigts. Ses mains restent loin. Ferdinand fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers maman. Maman est l'adulte dans la cuisine. Ferdinand dit : maman, je suis en colère. Maman écoute. La colère a un nom. Les mains restent loin. Plus tard, ils dessineront ensemble. Clara rend le crayon. Ferdinand reprend un trait bleu.</t>
+          <t>Ferdinand dessine un bateau à la table. Maman coupe des carottes. Le crayon bleu glisse. Sa sœur Clara prend le crayon. Ferdinand sent son visage chaud. Son ventre est dur. Je suis en colère. Il ouvre les doigts. Ses mains restent loin. Ferdinand fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers maman. Maman est l'adulte dans la cuisine. Maman, je suis en colère. Maman écoute. La colère a un nom. Les mains restent loin. Plus tard, ils dessineront ensemble. Clara rend le crayon. Ferdinand reprend un trait bleu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ferdinand dessine un bateau à la table. Maman coupe des carottes. Le crayon bleu glisse. Sa sœur Clara prend le crayon. Ferdinand sent son visage chaud. Son ventre est dur.
+enfant-m|Je suis en colère. Il ouvre les doigts. Ses mains restent loin.
+narrateur|Ferdinand fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers maman. Maman est l'adulte dans la cuisine.
+enfant-m|Maman, je suis en colère. Maman écoute.
+narrateur|La colère a un nom. Les mains restent loin. Plus tard, ils dessineront ensemble. Clara rend le crayon. Ferdinand reprend un trait bleu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Ferdinand est en colère. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ferdinand a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers maman, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Ferdinand s'assoit près de maman. Les carottes restent dans le saladier.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|La colère a un nom. Les mains restent loin. Plus tard, ils dessineront ensemble. Clara rend le crayon. Ferdinand reprend un trait bleu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Ferdinand est en colère. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Ferdinand a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers maman, l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Ferdinand s'assoit près de maman. Les carottes restent dans le saladier.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.005-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ferdinand nomme sa colère</t>
+          <t>Le crayon bleu de Nino</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,7 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +831,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino dessine un bateau. Mila prend le crayon bleu. Il nomme sa colère, ouvre les doigts, s'éloigne, rejoint maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ferdinand dessine un bateau à la table. Maman coupe des carottes. Le crayon bleu glisse. Sa sœur Clara prend le crayon. Ferdinand sent son visage chaud. Son ventre est dur. Je suis en colère. Il ouvre les doigts. Ses mains restent loin. Ferdinand fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers maman. Maman est l'adulte dans la cuisine. Maman, je suis en colère. Maman écoute. La colère a un nom. Les mains restent loin. Plus tard, ils dessineront ensemble. Clara rend le crayon. Ferdinand reprend un trait bleu.</t>
+          <t>La vapeur de la casserole tapote le carreau. Elle fait un nuage tout doux. Des pelures de carotte s'enroulent dans l'évier. Elles sont orange, un peu humides. La cuillère en bois tape le bord. Toc, toc, tout bas. La toile cirée est à petits pois. Un crayon bleu attend près de l'assiette. Nino, tu sens les carottes ? Oui, maman. Ça sent le chaud. Je coupe encore un peu. En ce moment, Nino dessine un bateau. Le papier est un peu rêche. Le bateau a une voile. Mila est là, près de la table. La mer, je la fais en bleu. Belle mer, Nino. Tu prends ton temps. La casserole chante tout bas. Le crayon bleu glisse. Mila le prend. Nino sent son visage chaud. Son ventre est dur. Parce que le crayon est parti. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Mila. Nino fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers maman. Maman est l'adulte dans la cuisine. Maman, je suis en colère. Le crayon bleu est parti. Tu as dit le nom. Tu es en colère. Bravo, Nino. Tes mains sont restées loin. Tu t'es éloigné. Tu es venu vers moi. Tu as fait du bon travail. Tu veux souffler encore ? Oui, maman. Nino souffle. La vapeur tapote encore le carreau. Tu veux rester près de moi un moment ? Oui, maman. La toile cirée est un peu tiède. Plus tard, ils dessineront ensemble. Mila rend le crayon. Nino reprend un trait bleu. La mer est revenue. Un petit trait, tout doux. La colère a un nom. Les mains restent loin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1325,63 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Ferdinand dessine un bateau à la table. Maman coupe des carottes. Le crayon bleu glisse. Sa sœur Clara prend le crayon. Ferdinand sent son visage chaud. Son ventre est dur.
-enfant-m|Je suis en colère. Il ouvre les doigts. Ses mains restent loin.
-narrateur|Ferdinand fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers maman. Maman est l'adulte dans la cuisine.
-enfant-m|Maman, je suis en colère. Maman écoute.
-narrateur|La colère a un nom. Les mains restent loin. Plus tard, ils dessineront ensemble. Clara rend le crayon. Ferdinand reprend un trait bleu.</t>
+          <t>narrateur|La vapeur de la casserole tapote le carreau.
+narrateur|Elle fait un nuage tout doux.
+narrateur|Des pelures de carotte s'enroulent dans l'évier.
+narrateur|Elles sont orange, un peu humides.
+narrateur|La cuillère en bois tape le bord.
+narrateur|Toc, toc, tout bas.
+narrateur|La toile cirée est à petits pois.
+narrateur|Un crayon bleu attend près de l'assiette.
+maman|Nino, tu sens les carottes ?
+enfant-m|Oui, maman.
+enfant-m|Ça sent le chaud.
+maman|Je coupe encore un peu.
+narrateur|En ce moment, Nino dessine un bateau.
+narrateur|Le papier est un peu rêche.
+narrateur|Le bateau a une voile.
+narrateur|Mila est là, près de la table.
+enfant-m|La mer, je la fais en bleu.
+maman|Belle mer, Nino.
+maman|Tu prends ton temps.
+narrateur|La casserole chante tout bas.
+narrateur|Le crayon bleu glisse.
+narrateur|Mila le prend.
+narrateur|Nino sent son visage chaud.
+narrateur|Son ventre est dur.
+narrateur|Parce que le crayon est parti.
+enfant-m|Je suis en colère.
+narrateur|Il ouvre les doigts.
+narrateur|Ses mains restent loin de Mila.
+narrateur|Nino fait un pas en arrière.
+narrateur|Il peut s'éloigner.
+narrateur|Il s'éloigne vers le canapé.
+narrateur|Il souffle trois fois.
+narrateur|Puis il va vers maman.
+narrateur|Maman est l'adulte dans la cuisine.
+enfant-m|Maman, je suis en colère.
+enfant-m|Le crayon bleu est parti.
+maman|Tu as dit le nom.
+maman|Tu es en colère.
+maman|Bravo, Nino.
+maman|Tes mains sont restées loin.
+maman|Tu t'es éloigné.
+maman|Tu es venu vers moi.
+maman|Tu as fait du bon travail.
+maman|Tu veux souffler encore ?
+enfant-m|Oui, maman.
+narrateur|Nino souffle.
+narrateur|La vapeur tapote encore le carreau.
+maman|Tu veux rester près de moi un moment ?
+enfant-m|Oui, maman.
+narrateur|La toile cirée est un peu tiède.
+narrateur|Plus tard, ils dessineront ensemble.
+narrateur|Mila rend le crayon.
+narrateur|Nino reprend un trait bleu.
+maman|La mer est revenue.
+enfant-m|Un petit trait, tout doux.
+narrateur|La colère a un nom.
+narrateur|Les mains restent loin.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ferdinand est en colère. Que fait-il ?</t>
+          <t>Nino est en colère. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1569,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Ferdinand est en colère. Que fait-il ?</t>
+          <t>narrateur|Nino est en colère.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1598,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ferdinand a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers maman, l'adulte.</t>
+          <t>Nino a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers maman, l'adulte. Tu as dit : je suis en colère. Bravo, Nino. J'ai ouvert les doigts. Oui. Et tu es venu vers moi. Tu as fait du bon travail. Les pelures restent dans l'évier. Le bateau attend sur le papier.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1742,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Ferdinand a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers maman, l'adulte.</t>
+          <t>narrateur|Nino a nommé sa colère.
+narrateur|Mains loin.
+narrateur|Il peut s'éloigner.
+narrateur|Il va vers maman, l'adulte.
+maman|Tu as dit : je suis en colère.
+maman|Bravo, Nino.
+enfant-m|J'ai ouvert les doigts.
+maman|Oui.
+maman|Et tu es venu vers moi.
+maman|Tu as fait du bon travail.
+narrateur|Les pelures restent dans l'évier.
+narrateur|Le bateau attend sur le papier.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1781,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ferdinand s'assoit près de maman. Les carottes restent dans le saladier.</t>
+          <t>Nino s'assoit près de maman. Les carottes restent dans le saladier. Tu veux un trait de plus ? Un tout petit. Le crayon bleu est tiède dans sa main. Tu as nommé ta colère. C'est du bon travail. La mer est un peu bleue, maintenant. On laisse sécher le dessin ? Oui, maman. La vapeur est plus petite. La cuillère en bois se tait.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1917,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ferdinand s'assoit près de maman. Les carottes restent dans le saladier.</t>
+          <t>narrateur|Nino s'assoit près de maman.
+narrateur|Les carottes restent dans le saladier.
+maman|Tu veux un trait de plus ?
+enfant-m|Un tout petit.
+narrateur|Le crayon bleu est tiède dans sa main.
+maman|Tu as nommé ta colère.
+maman|C'est du bon travail.
+enfant-m|La mer est un peu bleue, maintenant.
+maman|On laisse sécher le dessin ?
+enfant-m|Oui, maman.
+narrateur|La vapeur est plus petite.
+narrateur|La cuillère en bois se tait.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit : je suis en colère. Je me suis éloigné. Je suis allé vers maman. Bravo, Nino. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2096,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit : je suis en colère.
+enfant-m|Je me suis éloigné.
+enfant-m|Je suis allé vers maman.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-05.xlsx
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vapeur de la casserole tapote le carreau. Elle fait un nuage tout doux. Des pelures de carotte s'enroulent dans l'évier. Elles sont orange, un peu humides. La cuillère en bois tape le bord. Toc, toc, tout bas. La toile cirée est à petits pois. Un crayon bleu attend près de l'assiette. Nino, tu sens les carottes ? Oui, maman. Ça sent le chaud. Je coupe encore un peu. En ce moment, Nino dessine un bateau. Le papier est un peu rêche. Le bateau a une voile. Mila est là, près de la table. La mer, je la fais en bleu. Belle mer, Nino. Tu prends ton temps. La casserole chante tout bas. Le crayon bleu glisse. Mila le prend. Nino sent son visage chaud. Son ventre est dur. Parce que le crayon est parti. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Mila. Nino fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers maman. Maman est l'adulte dans la cuisine. Maman, je suis en colère. Le crayon bleu est parti. Tu as dit le nom. Tu es en colère. Bravo, Nino. Tes mains sont restées loin. Tu t'es éloigné. Tu es venu vers moi. Tu as fait du bon travail. Tu veux souffler encore ? Oui, maman. Nino souffle. La vapeur tapote encore le carreau. Tu veux rester près de moi un moment ? Oui, maman. La toile cirée est un peu tiède. Plus tard, ils dessineront ensemble. Mila rend le crayon. Nino reprend un trait bleu. La mer est revenue. Un petit trait, tout doux. La colère a un nom. Les mains restent loin.</t>
+          <t>La vapeur de la casserole tapote le carreau. Elle fait un nuage tout doux. Des pelures de carotte s'enroulent dans l'évier. Elles sont orange, un peu humides. La cuillère en bois tape le bord. Toc, toc, tout bas. La toile cirée est à petits pois. Un crayon bleu attend près de l'assiette. Nino, tu sens les carottes ? Oui, maman. Ça sent le chaud. Je coupe encore un peu. En ce moment, Nino dessine un bateau. Le papier est un peu rêche. Le bateau a une voile. Mila est là, près de la table. La mer, je la fais en bleu. Belle mer, Nino. Tu prends ton temps. La casserole chante tout bas. Le crayon bleu glisse. Mila le prend. Nino sent son visage chaud. Son ventre est dur. Parce que le crayon est parti. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Mila. Nino fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers maman. Maman est l'adulte dans la cuisine. Maman, je suis en colère. Le crayon bleu est parti. Tu as dit le nom. Tu es en colère. Bravo, Nino. Tes mains sont restées loin. Tu t'es éloigné. Tu es venu vers moi. Tu veux souffler encore ? Oui, maman. Nino souffle. La vapeur tapote encore le carreau. Tu veux rester près de moi un moment ? Oui, maman. La toile cirée est un peu tiède. Plus tard, ils dessineront ensemble. Mila rend le crayon. Nino reprend un trait bleu. La mer est revenue. Un petit trait, tout doux. La colère a un nom. Les mains restent loin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ferdinand dessine un bateau à la table. Maman coupe des carottes. Le crayon bleu glisse. Sa sœur Clara prend le crayon. Ferdinand sent son visage chaud. Son ventre est dur. Ferdinand dit : je suis en &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;. Il ouvre les doigts. Ses mains restent loin. Ferdinand fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers maman. Maman est l'adulte dans la cuisine. Ferdinand dit : maman, je suis en colère. Maman écoute. La colère a un nom. Les mains restent loin. Plus tard, ils dessineront ensemble. Clara rend le crayon. Ferdinand reprend un trait bleu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vapeur de la casserole tapote le carreau. Elle fait un nuage tout doux. Des pelures de carotte s'enroulent dans l'évier. Elles sont orange, un peu humides. La cuillère en bois tape le bord. Toc, toc, tout bas. La toile cirée est à petits pois. Un crayon bleu attend près de l'assiette. Nino, tu sens les carottes ? Oui, maman. Ça sent le chaud. Je coupe encore un peu. En ce moment, Nino dessine un bateau. Le papier est un peu rêche. Le bateau a une voile. Mila est là, près de la table. La mer, je la fais en bleu. Belle mer, Nino. Tu prends ton temps. La casserole chante tout bas. Le crayon bleu glisse. Mila le prend. Nino sent son visage chaud. Son ventre est dur. Parce que le crayon est parti. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Mila. Nino fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers maman. Maman est l'adulte dans la cuisine. Maman, je suis en colère. Le crayon bleu est parti. Tu as dit le nom. Tu es en colère. Bravo, Nino. Tes mains sont restées loin. Tu t'es éloigné. Tu es venu vers moi. Tu veux souffler encore ? Oui, maman. Nino souffle. La vapeur tapote encore le carreau. Tu veux rester près de moi un moment ? Oui, maman. La toile cirée est un peu tiède. Plus tard, ils dessineront ensemble. Mila rend le crayon. Nino reprend un trait bleu. La mer est revenue. Un petit trait, tout doux. La colère a un nom. Les mains restent loin.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1367,7 +1367,6 @@
 maman|Tes mains sont restées loin.
 maman|Tu t'es éloigné.
 maman|Tu es venu vers moi.
-maman|Tu as fait du bon travail.
 maman|Tu veux souffler encore ?
 enfant-m|Oui, maman.
 narrateur|Nino souffle.
@@ -1384,7 +1383,6 @@
 narrateur|Les mains restent loin.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1414,7 +1412,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ferdinand est en &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino est en colère. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1573,7 +1571,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1598,12 +1595,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers maman, l'adulte. Tu as dit : je suis en colère. Bravo, Nino. J'ai ouvert les doigts. Oui. Et tu es venu vers moi. Tu as fait du bon travail. Les pelures restent dans l'évier. Le bateau attend sur le papier.</t>
+          <t>Nino a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers maman, l'adulte. Tu as dit : je suis en colère. Bravo, Nino. J'ai ouvert les doigts. Oui. Et tu es venu vers moi. Les pelures restent dans l'évier. Le bateau attend sur le papier.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ferdinand a nommé sa &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;. Mains loin. Il peut s'éloigner. Il va vers maman, l'adulte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers maman, l'adulte. Tu as dit : je suis en colère. Bravo, Nino. J'ai ouvert les doigts. Oui. Et tu es venu vers moi. Les pelures restent dans l'évier. Le bateau attend sur le papier.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1751,12 +1748,10 @@
 enfant-m|J'ai ouvert les doigts.
 maman|Oui.
 maman|Et tu es venu vers moi.
-maman|Tu as fait du bon travail.
 narrateur|Les pelures restent dans l'évier.
 narrateur|Le bateau attend sur le papier.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1781,12 +1776,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino s'assoit près de maman. Les carottes restent dans le saladier. Tu veux un trait de plus ? Un tout petit. Le crayon bleu est tiède dans sa main. Tu as nommé ta colère. C'est du bon travail. La mer est un peu bleue, maintenant. On laisse sécher le dessin ? Oui, maman. La vapeur est plus petite. La cuillère en bois se tait.</t>
+          <t>Nino s'assoit près de maman. Les carottes restent dans le saladier. Tu veux un trait de plus ? Un tout petit. Le crayon bleu est tiède dans sa main. Tu as nommé ta colère. La mer est un peu bleue, maintenant. On laisse sécher le dessin ? Oui, maman. La vapeur est plus petite. La cuillère en bois se tait.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ferdinand s'assoit près de maman. Les carottes restent dans le saladier.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino s'assoit près de maman. Les carottes restent dans le saladier. Tu veux un trait de plus ? Un tout petit. Le crayon bleu est tiède dans sa main. Tu as nommé ta colère. La mer est un peu bleue, maintenant. On laisse sécher le dessin ? Oui, maman. La vapeur est plus petite. La cuillère en bois se tait.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1923,7 +1918,6 @@
 enfant-m|Un tout petit.
 narrateur|Le crayon bleu est tiède dans sa main.
 maman|Tu as nommé ta colère.
-maman|C'est du bon travail.
 enfant-m|La mer est un peu bleue, maintenant.
 maman|On laisse sécher le dessin ?
 enfant-m|Oui, maman.
@@ -1931,7 +1925,6 @@
 narrateur|La cuillère en bois se tait.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1956,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit : je suis en colère. Je me suis éloigné. Je suis allé vers maman. Bravo, Nino. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>J'ai dit : je suis en colère. Je me suis éloigné. Je suis allé vers maman. Bravo, Nino.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit : je suis en colère. Je me suis éloigné. Je suis allé vers maman. Bravo, Nino.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,12 +2092,9 @@
           <t>enfant-m|J'ai dit : je suis en colère.
 enfant-m|Je me suis éloigné.
 enfant-m|Je suis allé vers maman.
-maman|Bravo, Nino.
-maman|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo, Nino.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2158,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-05.xlsx
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ferdinand, Clara, maman</t>
+          <t>Nino, Mila, maman</t>
         </is>
       </c>
     </row>
